--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484727_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484727_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4733</v>
+        <v>0.6514</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5113</v>
+        <v>-0.1215</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9846</v>
+        <v>0.773</v>
       </c>
       <c r="G3" t="n">
         <v>1.6683</v>
@@ -688,13 +688,13 @@
         <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0694</v>
+        <v>0.2475</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3404</v>
+        <v>0.0493</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4098</v>
+        <v>0.1981</v>
       </c>
       <c r="V3" t="n">
         <v>0.6226</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2545</v>
+        <v>-1.2317</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3709</v>
+        <v>-2.6923</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1164</v>
+        <v>1.4606</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6995</v>
+        <v>-2.0372</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3469</v>
+        <v>-1.4032</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3526</v>
+        <v>-0.634</v>
       </c>
       <c r="J4" t="n">
-        <v>0.013</v>
+        <v>-0.3188</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1104</v>
+        <v>0.2073</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1234</v>
+        <v>-0.5262</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7125</v>
+        <v>-1.7184</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2365</v>
+        <v>-1.6106</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.476</v>
+        <v>-0.1078</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.887</v>
+        <v>2.6418</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4449</v>
+        <v>-0.5908</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5031</v>
+        <v>-0.4674</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0581</v>
+        <v>-0.1234</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.585</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6215</v>
+        <v>-1.414</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.0821</v>
+        <v>-1.3453</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4606</v>
+        <v>-0.0688</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0372</v>
+        <v>-1.6995</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4032</v>
+        <v>-1.3469</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.634</v>
+        <v>-0.3526</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3188</v>
+        <v>0.013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2073</v>
+        <v>-0.1104</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5262</v>
+        <v>0.1234</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7184</v>
+        <v>-1.7125</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6106</v>
+        <v>-1.2365</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1078</v>
+        <v>-0.476</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6418</v>
+        <v>1.887</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9805</v>
+        <v>0.2854</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8571</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1234</v>
+        <v>-0.2433</v>
       </c>
       <c r="V5" t="n">
-        <v>1.585</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1184</v>
+        <v>-1.7551</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.2659</v>
+        <v>-3.8762</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1475</v>
+        <v>2.121</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6673</v>
@@ -922,13 +922,13 @@
         <v>2.8305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8094</v>
+        <v>-0.4462</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0923</v>
+        <v>-0.7026</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2828</v>
+        <v>0.2564</v>
       </c>
       <c r="V6" t="n">
         <v>0.3018</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2735</v>
+        <v>-2.1697</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4077</v>
+        <v>-2.2578</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.6811</v>
+        <v>0.0881</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.7746</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0464</v>
+        <v>-1.2381</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5157</v>
+        <v>0.4635</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1661</v>
+        <v>0.1196</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0839</v>
+        <v>-0.5384</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0823</v>
+        <v>0.6581</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6968</v>
+        <v>-0.8942</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1302</v>
+        <v>-0.6996</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4334</v>
+        <v>-0.1946</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3774</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7476</v>
+        <v>-0.829</v>
       </c>
       <c r="T7" t="n">
-        <v>1.506</v>
+        <v>-0.4904</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2417</v>
+        <v>-0.3386</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.113</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.7356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4964</v>
+        <v>-2.4324</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5316</v>
+        <v>-2.9297</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0352</v>
+        <v>0.4973</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7746</v>
+        <v>-0.0459</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2381</v>
+        <v>-2.3642</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4635</v>
+        <v>2.3183</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1196</v>
+        <v>1.4897</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5384</v>
+        <v>0.2543</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6581</v>
+        <v>1.2354</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8942</v>
+        <v>-1.5356</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6996</v>
+        <v>-2.6185</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1946</v>
+        <v>1.083</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5661</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3209</v>
+        <v>2.4531</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1557</v>
+        <v>-1.0656</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7642</v>
+        <v>-0.6454</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3915</v>
+        <v>-0.4202</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.988</v>
+        <v>-2.6995</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8624</v>
+        <v>-1.7062</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1256</v>
+        <v>-0.9933</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7844</v>
@@ -1156,13 +1156,13 @@
         <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5244</v>
+        <v>-0.2359</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3527</v>
+        <v>-0.1965</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1716</v>
+        <v>-0.0394</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3018</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.232</v>
+        <v>-3.625</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7293</v>
+        <v>-3.3784</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4973</v>
+        <v>-0.2466</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0459</v>
+        <v>-3.866</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3642</v>
+        <v>-1.7358</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3183</v>
+        <v>-2.1302</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4897</v>
+        <v>-2.5918</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2543</v>
+        <v>-0.1581</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2354</v>
+        <v>-2.4337</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5356</v>
+        <v>-1.2742</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6185</v>
+        <v>-1.5777</v>
       </c>
       <c r="O10" t="n">
-        <v>1.083</v>
+        <v>0.3035</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4531</v>
+        <v>2.6418</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8652</v>
+        <v>-1.1554</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.445</v>
+        <v>-0.7675</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4202</v>
+        <v>-0.3879</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7652</v>
+        <v>-3.8232</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3599</v>
+        <v>0.1225</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4053</v>
+        <v>-3.9457</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.866</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7358</v>
+        <v>-1.0464</v>
       </c>
       <c r="I11" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.1661</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.0839</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0823</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.6968</v>
+      </c>
+      <c r="N11" t="n">
         <v>-2.1302</v>
       </c>
-      <c r="J11" t="n">
-        <v>-2.5918</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.1581</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-2.4337</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-1.2742</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-1.5777</v>
-      </c>
       <c r="O11" t="n">
-        <v>0.3035</v>
+        <v>0.4334</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6983</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6418</v>
+        <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2956</v>
+        <v>0.198</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.749</v>
+        <v>0.2208</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5466</v>
+        <v>-0.0229</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3018</v>
+        <v>-3.113</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9244</v>
+        <v>0.6226</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2262</v>
+        <v>-3.7356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>H. ENGUIX TORMO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7339</v>
+        <v>-5.3159</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4981</v>
+        <v>-0.6311</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2358</v>
+        <v>-4.6848</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.965</v>
+        <v>-1.2936</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6816</v>
+        <v>-2.2226</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2834</v>
+        <v>0.929</v>
       </c>
       <c r="J12" t="n">
-        <v>0.596</v>
+        <v>1.1013</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5548999999999999</v>
+        <v>-0.1738</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0411</v>
+        <v>1.275</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.561</v>
+        <v>-2.3949</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2365</v>
+        <v>-2.0488</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3245</v>
+        <v>-0.3461</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.6418</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.774</v>
+        <v>-1.887</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2592</v>
+        <v>-0.8902</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3215</v>
+        <v>-0.1472</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5808</v>
+        <v>-0.743</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8678</v>
+        <v>-2.1886</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3018</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2262</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. ENGUIX TORMO</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.1646</v>
+        <v>-5.4777</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2946</v>
+        <v>-3.4006</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.87</v>
+        <v>-2.077</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2936</v>
+        <v>-0.965</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.2226</v>
+        <v>-0.6816</v>
       </c>
       <c r="I13" t="n">
-        <v>0.929</v>
+        <v>-0.2834</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1013</v>
+        <v>0.596</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1738</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.275</v>
+        <v>0.0411</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3949</v>
+        <v>-1.561</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0488</v>
+        <v>-1.2365</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3461</v>
+        <v>-0.3245</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9435</v>
+        <v>-2.6418</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7389</v>
+        <v>-0.0031</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8107</v>
+        <v>0.4189</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9282</v>
+        <v>-0.422</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1886</v>
+        <v>-1.8678</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4904</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.2238</v>
+        <v>-28.3419</v>
       </c>
       <c r="E14" t="n">
-        <v>-22.1475</v>
+        <v>-21.2657</v>
       </c>
       <c r="F14" t="n">
         <v>-7.0762</v>
@@ -1522,7 +1522,7 @@
         <v>4.2954</v>
       </c>
       <c r="K14" t="n">
-        <v>1.807600000000001</v>
+        <v>1.8076</v>
       </c>
       <c r="L14" t="n">
         <v>2.4878</v>
@@ -1534,7 +1534,7 @@
         <v>-15.1274</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2128999999999998</v>
+        <v>-0.2128999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-7.548</v>
@@ -1546,13 +1546,13 @@
         <v>18.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.367</v>
+        <v>-4.4853</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.0808</v>
+        <v>-2.1993</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2861</v>
+        <v>-2.2862</v>
       </c>
       <c r="V14" t="n">
         <v>-5.2636</v>
@@ -1561,13 +1561,13 @@
         <v>3.056</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.319600000000001</v>
+        <v>-8.319599999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.5751</v>
+        <v>5.6364</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9265</v>
+        <v>3.7031</v>
       </c>
       <c r="F15" t="n">
-        <v>4.6486</v>
+        <v>1.9333</v>
       </c>
       <c r="G15" t="n">
-        <v>4.835</v>
+        <v>4.9938</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8629</v>
+        <v>1.6818</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9721</v>
+        <v>3.312</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2992</v>
+        <v>6.0621</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4354</v>
+        <v>2.8369</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8637</v>
+        <v>3.2252</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5358</v>
+        <v>-1.0683</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4275</v>
+        <v>-1.1551</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1083</v>
+        <v>0.0868</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2644</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.7175</v>
+        <v>-2.8305</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4531</v>
+        <v>2.8305</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0991</v>
+        <v>0.6427</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4394</v>
+        <v>0.4716</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6597</v>
+        <v>0.1711</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9054</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9054</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.461</v>
+        <v>5.4412</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3838</v>
+        <v>0.5881</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0772</v>
+        <v>4.8532</v>
       </c>
       <c r="G16" t="n">
-        <v>4.114</v>
+        <v>4.835</v>
       </c>
       <c r="H16" t="n">
-        <v>2.696</v>
+        <v>3.8629</v>
       </c>
       <c r="I16" t="n">
-        <v>1.418</v>
+        <v>0.9721</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8185</v>
+        <v>3.2992</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7946</v>
+        <v>2.4354</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0239</v>
+        <v>0.8637</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7045</v>
+        <v>1.5358</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.09859999999999999</v>
+        <v>1.4275</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6059</v>
+        <v>0.1083</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1887</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.887</v>
+        <v>-4.7175</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0757</v>
+        <v>2.4531</v>
       </c>
       <c r="S16" t="n">
-        <v>3.045</v>
+        <v>1.9652</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0938</v>
+        <v>1.101</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9512</v>
+        <v>0.8642</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8868</v>
+        <v>0.9054</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.9054</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6922</v>
+        <v>4.2844</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0211</v>
+        <v>1.6302</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6711</v>
+        <v>2.6542</v>
       </c>
       <c r="G17" t="n">
-        <v>4.9938</v>
+        <v>3.1142</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6818</v>
+        <v>1.6075</v>
       </c>
       <c r="I17" t="n">
-        <v>3.312</v>
+        <v>1.5068</v>
       </c>
       <c r="J17" t="n">
-        <v>6.0621</v>
+        <v>3.4958</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8369</v>
+        <v>2.0973</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2252</v>
+        <v>1.3984</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0683</v>
+        <v>-0.3815</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1551</v>
+        <v>-0.4899</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0868</v>
+        <v>0.1083</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8305</v>
+        <v>2.6418</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3016</v>
+        <v>0.4153</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2105</v>
+        <v>0.0214</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0911</v>
+        <v>0.3939</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1891</v>
+        <v>4.2349</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6451</v>
+        <v>2.0348</v>
       </c>
       <c r="F18" t="n">
-        <v>2.544</v>
+        <v>2.2001</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4049</v>
@@ -1858,13 +1858,13 @@
         <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3486</v>
+        <v>1.3944</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0864</v>
+        <v>0.4761</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2622</v>
+        <v>0.9183</v>
       </c>
       <c r="V18" t="n">
         <v>0.6036</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.1689</v>
+        <v>4.0801</v>
       </c>
       <c r="E19" t="n">
-        <v>1.825</v>
+        <v>3.2146</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3438</v>
+        <v>0.8656</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1142</v>
+        <v>4.114</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6075</v>
+        <v>2.696</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5068</v>
+        <v>1.418</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4958</v>
+        <v>4.8185</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0973</v>
+        <v>2.7946</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3984</v>
+        <v>2.0239</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3815</v>
+        <v>-0.7045</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4899</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1083</v>
+        <v>-0.6059</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>2.0757</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2998</v>
+        <v>1.6642</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2163</v>
+        <v>0.9246</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0835</v>
+        <v>0.7396</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8868</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8689</v>
+        <v>2.9719</v>
       </c>
       <c r="E20" t="n">
-        <v>0.152</v>
+        <v>0.8341</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7169</v>
+        <v>2.1378</v>
       </c>
       <c r="G20" t="n">
         <v>2.3336</v>
@@ -2014,13 +2014,13 @@
         <v>1.887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1246</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2105</v>
+        <v>0.4716</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0859</v>
+        <v>0.5068</v>
       </c>
       <c r="V20" t="n">
         <v>2.4904</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5198</v>
+        <v>2.6998</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1572</v>
+        <v>-0.4752</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6771</v>
+        <v>3.175</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5235</v>
@@ -2092,13 +2092,13 @@
         <v>2.8305</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4097</v>
+        <v>-0.2297</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0458</v>
+        <v>-0.3638</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3638</v>
+        <v>0.1341</v>
       </c>
       <c r="V21" t="n">
         <v>1.566</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5847</v>
+        <v>1.4001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1384</v>
+        <v>-1.0233</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4464</v>
+        <v>2.4233</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2828</v>
+        <v>-1.0096</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9994</v>
+        <v>-0.0415</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2834</v>
+        <v>-0.9681</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9607</v>
+        <v>-1.4517</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9195</v>
+        <v>-0.7865</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0411</v>
+        <v>-0.6651</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2434</v>
+        <v>0.4421</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9189</v>
+        <v>0.7451</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3245</v>
+        <v>-0.303</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1692</v>
+        <v>0.334</v>
       </c>
       <c r="T22" t="n">
-        <v>0.442</v>
+        <v>-0.1751</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7272</v>
+        <v>0.5091</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6226</v>
+        <v>0.9434</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3208</v>
+        <v>1.547</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1937</v>
+        <v>0.4611</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7053</v>
+        <v>-2.0223</v>
       </c>
       <c r="F23" t="n">
-        <v>1.899</v>
+        <v>2.4834</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0096</v>
+        <v>-1.9436</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0415</v>
+        <v>0.306</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9681</v>
+        <v>-2.2496</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4517</v>
+        <v>-1.5734</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7865</v>
+        <v>0.8929</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6651</v>
+        <v>-2.4663</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4421</v>
+        <v>-0.3702</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7451</v>
+        <v>-0.5869</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.303</v>
+        <v>0.2167</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1322</v>
+        <v>3.2079</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0757</v>
+        <v>3.2079</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8724</v>
+        <v>-0.1996</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8571</v>
+        <v>-0.4489</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0152</v>
+        <v>0.2493</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9434</v>
+        <v>-0.6036</v>
       </c>
       <c r="W23" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-0.6036</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4363</v>
+        <v>0.1253</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6069</v>
+        <v>-0.0565</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1706</v>
+        <v>0.1818</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9436</v>
+        <v>-1.2828</v>
       </c>
       <c r="H24" t="n">
-        <v>0.306</v>
+        <v>-0.9994</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2496</v>
+        <v>-0.2834</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5734</v>
+        <v>0.9607</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8929</v>
+        <v>0.9195</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.4663</v>
+        <v>0.0411</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3702</v>
+        <v>-2.2434</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5869</v>
+        <v>-1.9189</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2167</v>
+        <v>-0.3245</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2079</v>
+        <v>1.3209</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
-        <v>3.2079</v>
+        <v>2.2644</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0969</v>
+        <v>0.7098</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0335</v>
+        <v>0.2471</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0634</v>
+        <v>0.4627</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6036</v>
+        <v>-0.6226</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5934</v>
+        <v>-0.1628</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5463</v>
+        <v>-1.3514</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9529</v>
+        <v>1.1886</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1813</v>
@@ -2404,13 +2404,13 @@
         <v>1.5096</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7895</v>
+        <v>-0.3589</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6343</v>
+        <v>-0.4395</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1552</v>
+        <v>0.0806</v>
       </c>
       <c r="V25" t="n">
         <v>1.8678</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>29.2237</v>
+        <v>31.17239999999999</v>
       </c>
       <c r="E26" t="n">
         <v>7.0762</v>
       </c>
       <c r="F26" t="n">
-        <v>22.1476</v>
+        <v>24.0963</v>
       </c>
       <c r="G26" t="n">
         <v>11.0449</v>
@@ -2482,19 +2482,19 @@
         <v>26.418</v>
       </c>
       <c r="S26" t="n">
-        <v>5.367</v>
+        <v>7.3157</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2862</v>
+        <v>2.2861</v>
       </c>
       <c r="U26" t="n">
-        <v>3.081</v>
+        <v>5.0297</v>
       </c>
       <c r="V26" t="n">
-        <v>5.2636</v>
+        <v>5.263599999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>8.319600000000001</v>
+        <v>8.319599999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-3.056</v>
